--- a/backend/PC_Specs.xlsx
+++ b/backend/PC_Specs.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -558,6 +558,63 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-08 09:18:44</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Windows OS (4 Logical Cores)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Auto-Detected System</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Windows OS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4 Logical Cores</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>~8 GB RAM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ANGLE (Intel, Intel(R) HD Graphics 4400 (0x0000041E) Direct3D11 vs_5_0 ps_5_0, D3D11)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1366 x 768 (1x Scale, 24-bit)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pune, Maharashtra, India (Proline Datatech Services Pvt. Ltd.)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Google Chrome</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>103.177.236.220</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/PC_Specs.xlsx
+++ b/backend/PC_Specs.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -615,6 +615,63 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-08 09:26:13</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Windows OS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4 Logical Cores</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>~8 GB RAM</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ANGLE (Intel, Intel(R) HD Graphics 4400 (0x0000041E) Direct3D11 vs_5_0 ps_5_0, D3D11)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1366 x 768 (1x Scale, 24-bit)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pune, Maharashtra, India (Proline Datatech Services Pvt. Ltd.)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Google Chrome</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>103.177.236.220</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
